--- a/reports/pdf_change_20260727.xlsx
+++ b/reports/pdf_change_20260727.xlsx
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억   ·   현금 29억(0.7%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 2종목  /  매도 2종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,032억   ·   현금 30억(0.7%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>651656250</v>
+        <v>652312500</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-11</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-767886900</v>
+        <v>-768660200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>814756500</v>
+        <v>815577000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-5</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-700065000</v>
+        <v>-700770000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 14억(0.4%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,527억   ·   현금 13억(0.4%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -773,528 +773,948 @@
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
-      <c r="J14" s="19" t="n"/>
-      <c r="K14" s="19" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 290억   ·   현금 0억(0.1%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 5종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,302억   ·   현금 33억(1.4%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 2종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>2570503200</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>1.87%→3.17%</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>148→230</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>-395367280</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.18%</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>99→50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>1837536800</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>1.78%→2.61%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>76→110</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-2825436000</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>7.28%→5.79%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>170→140</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-388385000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>0.37%→0.17%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>50→25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,238억   ·   현금 8억(0.3%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 5종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>브이엠</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>74419200</v>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>3.32%→3.58%</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>156→168</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>코오롱티슈진  (편출)</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>-77</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>-123184600</v>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>0.42%→0.00%</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>77→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>82764000</v>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>2.75%→3.03%</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>87→96</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>-74100000</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>3.10%→2.84%</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>365→335</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>테스</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>81981200</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>2.90%→3.18%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>72→79</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>-80750000</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>7.68%→7.40%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>692→667</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>59660000</v>
+        <v>2309202000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.75%→2.95%</t>
+          <t>3.15%→3.95%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>67→72</t>
+          <t>296→401</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-11</v>
+        <v>-166</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-57684000</v>
+        <v>-10878710400</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.49%</t>
+          <t>14.17%→9.67%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>149→138</t>
+          <t>495→329</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>2404404000</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>3.09%→4.07%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>250→340</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>2446802100</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>5.05%→5.85%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>299→368</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>2585952000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>6.58%→7.46%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>348→412</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>2328574500</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>11.16%→11.93%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>219→240</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 0억(0.1%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 5종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>74419200</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>3.32%→3.58%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>156→168</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>코오롱티슈진  (편출)</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-123184600</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.00%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>77→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>82764000</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>2.75%→3.03%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>87→96</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-74100000</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>3.10%→2.84%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>365→335</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>81981200</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2.90%→3.18%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>72→79</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-80750000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>7.68%→7.40%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>692→667</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>59660000</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>2.75%→2.95%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>67→72</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-57684000</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>2.69%→2.49%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>149→138</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B35" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C35" s="11" t="n">
         <v>39550400</v>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>1.05%→1.19%</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>31→35</t>
         </is>
       </c>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 484억   ·   현금 8억(1.7%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 1종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 470억   ·   현금 8억(1.7%)      당일 2026-07-27  vs  전영업일 2026-07-24      매수 1종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>삼성바이오로직스  (신규)</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B40" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>505494000</v>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="C40" s="11" t="n">
+        <v>500940000</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.09%</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>0→3</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>큐리오시스  (편출)</t>
         </is>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H40" s="15" t="n">
         <v>-593</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>-746432820</v>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="I40" s="15" t="n">
+        <v>-739708200</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>1.54%→0.00%</t>
         </is>
       </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="K40" s="13" t="inlineStr">
         <is>
           <t>593→0</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="20" t="n"/>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="G29" s="14" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="18" t="n"/>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>코오롱티슈진  (편출)</t>
         </is>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H41" s="15" t="n">
         <v>-104</v>
       </c>
-      <c r="I29" s="15" t="n">
-        <v>-243001200</v>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="I41" s="15" t="n">
+        <v>-240812000</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>0.50%→0.00%</t>
         </is>
       </c>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t>104→0</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="20" t="n"/>
+      <c r="J43" s="20" t="n"/>
+      <c r="K43" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="G17:K17"/>
-    <mergeCell ref="G26:K26"/>
+  <mergeCells count="20">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A19:K19"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A9:K9"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260727.xlsx
+++ b/reports/pdf_change_20260727.xlsx
@@ -1321,11 +1321,11 @@
         <v>12</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>74419200</v>
+        <v>66849600</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>3.32%→3.58%</t>
+          <t>3.25%→3.50%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1342,11 +1342,11 @@
         <v>-77</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-123184600</v>
+        <v>-87780000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.00%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1365,11 +1365,11 @@
         <v>9</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>82764000</v>
+        <v>72435600</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>2.75%→3.03%</t>
+          <t>2.62%→2.89%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1386,11 +1386,11 @@
         <v>-30</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-74100000</v>
+        <v>-69312000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>3.10%→2.84%</t>
+          <t>3.16%→2.90%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1409,11 +1409,11 @@
         <v>7</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>81981200</v>
+        <v>72405200</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>2.90%→3.18%</t>
+          <t>2.79%→3.06%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1430,7 +1430,7 @@
         <v>-25</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-80750000</v>
+        <v>-74100000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1453,11 +1453,11 @@
         <v>5</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>59660000</v>
+        <v>54682000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>2.75%→2.95%</t>
+          <t>2.74%→2.95%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1474,11 +1474,11 @@
         <v>-11</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-57684000</v>
+        <v>-51999200</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.49%</t>
+          <t>2.64%→2.44%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1497,11 +1497,11 @@
         <v>4</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>39550400</v>
+        <v>34412800</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.19%</t>
+          <t>1.00%→1.13%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">

--- a/reports/pdf_change_20260727.xlsx
+++ b/reports/pdf_change_20260727.xlsx
@@ -1321,11 +1321,11 @@
         <v>12</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>66849600</v>
+        <v>81441600</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>3.25%→3.50%</t>
+          <t>3.76%→4.05%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1342,11 +1342,11 @@
         <v>-77</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-87780000</v>
+        <v>-251050800</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>0.89%→0.00%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1365,11 +1365,11 @@
         <v>9</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>72435600</v>
+        <v>92340000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.89%</t>
+          <t>3.17%→3.50%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1386,11 +1386,11 @@
         <v>-30</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-69312000</v>
+        <v>-65550000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>3.16%→2.90%</t>
+          <t>2.83%→2.60%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1409,11 +1409,11 @@
         <v>7</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>72405200</v>
+        <v>88152400</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>2.79%→3.06%</t>
+          <t>3.22%→3.54%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1430,11 +1430,11 @@
         <v>-25</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-74100000</v>
+        <v>-68780000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>7.68%→7.40%</t>
+          <t>6.76%→6.53%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1453,11 +1453,11 @@
         <v>5</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>54682000</v>
+        <v>64600000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.95%</t>
+          <t>3.07%→3.31%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1474,11 +1474,11 @@
         <v>-11</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-51999200</v>
+        <v>-46648800</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.64%→2.44%</t>
+          <t>2.24%→2.08%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1497,11 +1497,11 @@
         <v>4</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>34412800</v>
+        <v>43350400</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.13%</t>
+          <t>1.19%→1.35%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">

--- a/reports/pdf_change_20260727.xlsx
+++ b/reports/pdf_change_20260727.xlsx
@@ -1321,11 +1321,11 @@
         <v>12</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>81441600</v>
+        <v>66849600</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>3.76%→4.05%</t>
+          <t>3.25%→3.50%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1342,11 +1342,11 @@
         <v>-77</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-251050800</v>
+        <v>-87780000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.00%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1365,11 +1365,11 @@
         <v>9</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>92340000</v>
+        <v>72435600</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>3.17%→3.50%</t>
+          <t>2.62%→2.89%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1386,11 +1386,11 @@
         <v>-30</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-65550000</v>
+        <v>-69312000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>2.83%→2.60%</t>
+          <t>3.16%→2.90%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -1409,11 +1409,11 @@
         <v>7</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>88152400</v>
+        <v>72405200</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>3.22%→3.54%</t>
+          <t>2.79%→3.06%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1430,11 +1430,11 @@
         <v>-25</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-68780000</v>
+        <v>-74100000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>6.76%→6.53%</t>
+          <t>7.68%→7.40%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -1453,11 +1453,11 @@
         <v>5</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>64600000</v>
+        <v>54682000</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>3.07%→3.31%</t>
+          <t>2.74%→2.95%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1474,11 +1474,11 @@
         <v>-11</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-46648800</v>
+        <v>-51999200</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.24%→2.08%</t>
+          <t>2.64%→2.44%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1497,11 +1497,11 @@
         <v>4</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>43350400</v>
+        <v>34412800</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>1.19%→1.35%</t>
+          <t>1.00%→1.13%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
